--- a/Q2_结果.xlsx
+++ b/Q2_结果.xlsx
@@ -15,10 +15,10 @@
     <sheet name="汇总说明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q2_运输架次'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q2_运输架次'!$A$1:$H$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q2_逐箱交付'!$A$1:$D$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'架次物理校验'!$A$1:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'资源占用校验'!$A$1:$F$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'架次物理校验'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'资源占用校验'!$A$1:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'时限核验'!$A$1:$H$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'汇总说明'!$A$1:$B$10</definedName>
   </definedNames>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,14 +496,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1653.853569215474</v>
+        <v>2007.732659143701</v>
       </c>
       <c r="H2" t="n">
-        <v>1.979285860910201</v>
+        <v>2.929134125680061</v>
       </c>
     </row>
     <row r="3">
@@ -532,14 +532,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1612.024508122992</v>
+        <v>1653.853569215474</v>
       </c>
       <c r="H3" t="n">
-        <v>1.984884983905938</v>
+        <v>1.952542207648345</v>
       </c>
     </row>
     <row r="4">
@@ -568,14 +568,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2110.416386028363</v>
+        <v>1612.024508122992</v>
       </c>
       <c r="H4" t="n">
-        <v>3.002473149954873</v>
+        <v>1.957748064441923</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         <v>1988.962351014692</v>
       </c>
       <c r="H5" t="n">
-        <v>2.317936921147821</v>
+        <v>2.287653461780387</v>
       </c>
     </row>
     <row r="6">
@@ -640,14 +640,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1819.890041865742</v>
+        <v>1636.191043136609</v>
       </c>
       <c r="H6" t="n">
-        <v>2.798212858714431</v>
+        <v>1.779798350974533</v>
       </c>
     </row>
     <row r="7">
@@ -676,14 +676,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1636.191043136609</v>
+        <v>1923.801400652118</v>
       </c>
       <c r="H7" t="n">
-        <v>1.826315596919774</v>
+        <v>2.755237906410221</v>
       </c>
     </row>
     <row r="8">
@@ -719,7 +719,7 @@
         <v>1561.426741698547</v>
       </c>
       <c r="H8" t="n">
-        <v>2.976120742061005</v>
+        <v>2.92627284583651</v>
       </c>
     </row>
     <row r="9">
@@ -755,7 +755,7 @@
         <v>1560.863885273963</v>
       </c>
       <c r="H9" t="n">
-        <v>2.732146854650997</v>
+        <v>2.593979284603349</v>
       </c>
     </row>
     <row r="10">
@@ -791,7 +791,7 @@
         <v>3188.29062697251</v>
       </c>
       <c r="H10" t="n">
-        <v>3.031909089609012</v>
+        <v>3.004697890001106</v>
       </c>
     </row>
     <row r="11">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3606.434868281085</v>
+        <v>3672.434868281085</v>
       </c>
       <c r="H11" t="n">
-        <v>6.069552815880808</v>
+        <v>6.125027879101074</v>
       </c>
     </row>
     <row r="12">
@@ -838,7 +838,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -856,14 +856,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S013→S012</t>
+          <t>S010→S014</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3950.476447194515</v>
+        <v>3866.556650523419</v>
       </c>
       <c r="H12" t="n">
-        <v>3.032133134269779</v>
+        <v>2.479565703531253</v>
       </c>
     </row>
     <row r="13">
@@ -874,7 +874,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -899,7 +899,7 @@
         <v>3212.382086273218</v>
       </c>
       <c r="H13" t="n">
-        <v>1.71829202972833</v>
+        <v>1.656285556037786</v>
       </c>
     </row>
     <row r="14">
@@ -910,7 +910,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -928,14 +928,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S010→S014</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3908.385711615901</v>
+        <v>3205.878077338466</v>
       </c>
       <c r="H14" t="n">
-        <v>2.51744990024193</v>
+        <v>1.871042077364874</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +946,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1819.890041865742</v>
+        <v>1923.801400652118</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3900.132853916969</v>
+        <v>4004.044212703345</v>
       </c>
       <c r="H15" t="n">
-        <v>2.853669949807157</v>
+        <v>2.779171039452936</v>
       </c>
     </row>
     <row r="16">
@@ -992,7 +992,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1000,14 +1000,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5392.050516391937</v>
+        <v>5493.476118440301</v>
       </c>
       <c r="H16" t="n">
-        <v>6.208195835545007</v>
+        <v>6.17691902989136</v>
       </c>
     </row>
     <row r="17">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1043,7 +1043,7 @@
         <v>5041.956187289227</v>
       </c>
       <c r="H17" t="n">
-        <v>2.372661900043959</v>
+        <v>2.310905562967101</v>
       </c>
     </row>
     <row r="18">
@@ -1064,22 +1064,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3606.434868281085</v>
+        <v>3672.434868281085</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5779.620359748877</v>
+        <v>5876.194757700512</v>
       </c>
       <c r="H18" t="n">
-        <v>5.771310040262535</v>
+        <v>5.857497107796528</v>
       </c>
     </row>
     <row r="19">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3900.132853916969</v>
+        <v>4004.044212703345</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5825.905289964839</v>
+        <v>5564.824003250455</v>
       </c>
       <c r="H19" t="n">
-        <v>2.784494734796728</v>
+        <v>2.102455644233721</v>
       </c>
     </row>
     <row r="20">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1144,14 +1144,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6602.735977836337</v>
+        <v>6231.586991853713</v>
       </c>
       <c r="H20" t="n">
-        <v>2.161170561805987</v>
+        <v>1.077172635206365</v>
       </c>
     </row>
     <row r="21">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5392.050516391937</v>
+        <v>5493.476118440301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>7761.861374504362</v>
+        <v>7863.286976552727</v>
       </c>
       <c r="H21" t="n">
-        <v>6.085818119129903</v>
+        <v>5.763372389063068</v>
       </c>
     </row>
     <row r="22">
@@ -1198,72 +1198,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5825.905289964839</v>
+        <v>6164.62991887096</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7012.58409664521</v>
+        <v>8044.675535967012</v>
       </c>
       <c r="H22" t="n">
-        <v>1.104895989334458</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q2-022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>C-BAT-04</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6083.605422582137</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>7963.65103967819</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4.469072265539591</v>
+        <v>4.23878004069446</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H23"/>
+  <autoFilter ref="A1:H22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1302,7 +1266,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S010-MED-01</t>
+          <t>S002-MED-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1312,17 +1276,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1104.463451274404</v>
+        <v>1285.80632957185</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S010-WAT-01</t>
+          <t>S002-WAT-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1332,17 +1296,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1104.463451274404</v>
+        <v>1285.80632957185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S013-MED-01</t>
+          <t>S010-MED-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1352,17 +1316,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1083.545587394829</v>
+        <v>1104.463451274404</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S013-WAT-01</t>
+          <t>S010-WAT-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1372,17 +1336,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1083.545587394829</v>
+        <v>1104.463451274404</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S012-MED-01</t>
+          <t>S013-MED-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1392,17 +1356,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1335.138193014182</v>
+        <v>1083.545587394829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S012-WAT-01</t>
+          <t>S013-WAT-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1412,11 +1376,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1335.138193014182</v>
+        <v>1083.545587394829</v>
       </c>
     </row>
     <row r="8">
@@ -1462,7 +1426,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S002-FOD-01</t>
+          <t>S007-FOD-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1472,17 +1436,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1221.885020932871</v>
+        <v>1125.735521568304</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S002-MED-01</t>
+          <t>S007-MED-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1492,17 +1456,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1221.885020932871</v>
+        <v>1125.735521568304</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S002-WAT-01</t>
+          <t>S007-WAT-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1512,17 +1476,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1221.885020932871</v>
+        <v>1125.735521568304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S007-FOD-01</t>
+          <t>S012-FOD-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1532,17 +1496,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1125.735521568304</v>
+        <v>1271.830700326059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S012-MED-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1552,17 +1516,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1125.735521568304</v>
+        <v>1271.830700326059</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S007-WAT-01</t>
+          <t>S012-WAT-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1572,11 +1536,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1125.735521568304</v>
+        <v>1271.830700326059</v>
       </c>
     </row>
     <row r="16">
@@ -2002,7 +1966,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S002-FOD-02</t>
+          <t>S002-FOD-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2016,13 +1980,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S002-FOD-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2036,13 +2000,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S002-WAT-02</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2056,13 +2020,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S002-WAT-03</t>
+          <t>S002-WAT-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2076,13 +2040,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S002-WAT-04</t>
+          <t>S002-WAT-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2096,33 +2060,33 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S012-FOD-01</t>
+          <t>S002-WAT-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3175.198254180334</v>
+        <v>3050.340804989816</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S013-FOD-01</t>
+          <t>S010-FOD-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2132,37 +2096,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2665.570095517821</v>
+        <v>2686.487959397396</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S014-FOD-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2701.926564704913</v>
+        <v>3149.63214168274</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S007-WAT-02</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2182,27 +2146,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S010-FOD-01</t>
+          <t>S007-WAT-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2728.317020489878</v>
+        <v>2701.926564704913</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S014-FOD-01</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2212,11 +2176,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3191.461202775222</v>
+        <v>2677.399156610303</v>
       </c>
     </row>
     <row r="48">
@@ -2236,7 +2200,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3167.984781224689</v>
+        <v>3271.896140011065</v>
       </c>
     </row>
     <row r="49">
@@ -2256,7 +2220,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3167.984781224689</v>
+        <v>3271.896140011065</v>
       </c>
     </row>
     <row r="50">
@@ -2276,13 +2240,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3167.984781224689</v>
+        <v>3271.896140011065</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S004-FOD-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2292,17 +2256,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S004-HYG-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2312,17 +2276,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S008-MED-01</t>
+          <t>S004-MED-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2332,17 +2296,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S008-WAT-01</t>
+          <t>S004-WAT-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,17 +2316,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S008-WAT-02</t>
+          <t>S004-WAT-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2372,37 +2336,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S015-FOD-01</t>
+          <t>S004-WAT-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4430.609136781222</v>
+        <v>4773.853372706406</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
+          <t>S015-FOD-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2422,7 +2386,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2442,27 +2406,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S004-FOD-01</t>
+          <t>S015-WAT-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5059.997614014981</v>
+        <v>4430.609136781222</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S004-MED-01</t>
+          <t>S008-FOD-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2472,17 +2436,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5059.997614014981</v>
+        <v>5172.154812990799</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S004-WAT-02</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2492,17 +2456,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5059.997614014981</v>
+        <v>5172.154812990799</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S004-WAT-03</t>
+          <t>S008-MED-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2512,51 +2476,51 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5059.997614014981</v>
+        <v>5172.154812990799</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S004-HYG-01</t>
+          <t>S008-WAT-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5144.66573860757</v>
+        <v>5172.154812990799</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S004-WAT-01</t>
+          <t>S008-WAT-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5144.66573860757</v>
+        <v>5172.154812990799</v>
       </c>
     </row>
     <row r="65">
@@ -2567,7 +2531,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2576,7 +2540,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6133.936082562783</v>
+        <v>5096.0241079769</v>
       </c>
     </row>
     <row r="66">
@@ -2587,7 +2551,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2596,7 +2560,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6133.936082562783</v>
+        <v>5096.0241079769</v>
       </c>
     </row>
     <row r="67">
@@ -2607,7 +2571,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2616,73 +2580,73 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6133.936082562783</v>
+        <v>5096.0241079769</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S003-FOD-02</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6971.41594544815</v>
+        <v>5948.958256238137</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
+          <t>S011-MED-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6971.41594544815</v>
+        <v>5948.958256238137</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S003-WAT-02</t>
+          <t>S011-WAT-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6971.41594544815</v>
+        <v>5948.958256238137</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S003-WAT-03</t>
+          <t>S003-FOD-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2696,13 +2660,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6971.41594544815</v>
+        <v>7072.841547496514</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S003-WAT-04</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2716,67 +2680,67 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6971.41594544815</v>
+        <v>7072.841547496514</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S011-FOD-01</t>
+          <t>S003-WAT-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6731.431359971691</v>
+        <v>7072.841547496514</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S011-MED-01</t>
+          <t>S003-WAT-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6731.431359971691</v>
+        <v>7072.841547496514</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S011-WAT-01</t>
+          <t>S003-WAT-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6731.431359971691</v>
+        <v>7072.841547496514</v>
       </c>
     </row>
     <row r="76">
@@ -2787,7 +2751,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2796,7 +2760,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
     </row>
     <row r="77">
@@ -2807,7 +2771,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2816,7 +2780,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
     </row>
     <row r="78">
@@ -2827,7 +2791,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2836,7 +2800,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
     </row>
     <row r="79">
@@ -2847,7 +2811,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2856,7 +2820,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
     </row>
     <row r="80">
@@ -2867,7 +2831,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2876,7 +2840,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
     </row>
     <row r="81">
@@ -2887,7 +2851,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2896,7 +2860,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
     </row>
   </sheetData>
@@ -2911,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2959,7 +2923,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S010-MED-01,S010-WAT-01</t>
+          <t>S002-MED-01,S002-WAT-01</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2969,14 +2933,14 @@
         <v>0.039</v>
       </c>
       <c r="E2" t="n">
-        <v>56.01586975755109</v>
+        <v>34.90813054044308</v>
       </c>
       <c r="F2" t="n">
-        <v>2725.64726236731</v>
+        <v>3353.926962117941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>O01→S010(17.0kg,534.5s,1.0969kWh,435.6m); S010→O01(0.0kg,549.4s,0.8824kWh,435.6m)</t>
+          <t>O01→S002(17.0kg,715.8s,1.5671kWh,309.0m); S002→O01(0.0kg,721.9s,1.3620kWh,309.0m)</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2952,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S013-MED-01,S013-WAT-01</t>
+          <t>S010-MED-01,S010-WAT-01</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2998,14 +2962,14 @@
         <v>0.039</v>
       </c>
       <c r="E3" t="n">
-        <v>55.89144480209028</v>
+        <v>56.61017316337011</v>
       </c>
       <c r="F3" t="n">
-        <v>2685.435725695818</v>
+        <v>2717.921318091663</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>O01→S013(17.0kg,513.5s,1.0995kWh,399.2m); S013→O01(0.0kg,528.5s,0.8853kWh,399.2m)</t>
+          <t>O01→S010(17.0kg,534.5s,1.0702kWh,435.6m); S010→O01(0.0kg,549.4s,0.8824kWh,435.6m)</t>
         </is>
       </c>
     </row>
@@ -3017,7 +2981,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S012-MED-01,S012-WAT-01</t>
+          <t>S013-MED-01,S013-WAT-01</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3027,14 +2991,14 @@
         <v>0.039</v>
       </c>
       <c r="E4" t="n">
-        <v>33.27837444544728</v>
+        <v>56.49448745684615</v>
       </c>
       <c r="F4" t="n">
-        <v>3477.797518237549</v>
+        <v>2677.596171183992</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>O01→S012(17.0kg,765.1s,1.6354kWh,413.3m); S012→O01(0.0kg,775.3s,1.3671kWh,413.3m)</t>
+          <t>O01→S013(17.0kg,513.5s,1.0724kWh,399.2m); S013→O01(0.0kg,528.5s,0.8853kWh,399.2m)</t>
         </is>
       </c>
     </row>
@@ -3056,14 +3020,14 @@
         <v>0.039</v>
       </c>
       <c r="E5" t="n">
-        <v>48.49029064115953</v>
+        <v>49.16325640488029</v>
       </c>
       <c r="F5" t="n">
-        <v>3158.588572679618</v>
+        <v>3149.840017751248</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>O01→S014(17.0kg,702.0s,1.2801kWh,591.9m); S014→O01(0.0kg,716.9s,1.0378kWh,591.9m)</t>
+          <t>O01→S014(17.0kg,702.0s,1.2499kWh,591.9m); S014→O01(0.0kg,716.9s,1.0378kWh,591.9m)</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3039,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S002-MED-01,S002-WAT-01,S002-FOD-01</t>
+          <t>S007-MED-01,S007-WAT-01,S007-FOD-01</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3085,14 +3049,14 @@
         <v>0.067</v>
       </c>
       <c r="E6" t="n">
-        <v>30.04467853213924</v>
+        <v>55.50504122563667</v>
       </c>
       <c r="F6" t="n">
-        <v>3699.115613975328</v>
+        <v>3074.10366189224</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>O01→S002(25.0kg,591.9s,1.7140kWh,309.0m); S002→O01(0.0kg,598.0s,1.0842kWh,309.0m)</t>
+          <t>O01→S007(25.0kg,495.7s,1.0919kWh,512.0m); S007→O01(0.0kg,510.5s,0.6879kWh,512.0m)</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3068,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S007-MED-01,S007-WAT-01,S007-FOD-01</t>
+          <t>S012-MED-01,S012-WAT-01,S012-FOD-01</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3114,14 +3078,14 @@
         <v>0.067</v>
       </c>
       <c r="E7" t="n">
-        <v>54.34211007700564</v>
+        <v>31.11905233974447</v>
       </c>
       <c r="F7" t="n">
-        <v>3094.261135135178</v>
+        <v>3784.40449342988</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>O01→S007(25.0kg,495.7s,1.1384kWh,512.0m); S007→O01(0.0kg,510.5s,0.6879kWh,512.0m)</t>
+          <t>O01→S012(25.0kg,641.8s,1.6655kWh,413.3m); S012→O01(0.0kg,652.0s,1.0898kWh,413.3m)</t>
         </is>
       </c>
     </row>
@@ -3143,14 +3107,14 @@
         <v>0.159</v>
       </c>
       <c r="E8" t="n">
-        <v>62.79849072423745</v>
+        <v>63.42158942704362</v>
       </c>
       <c r="F8" t="n">
-        <v>3200.792776006735</v>
+        <v>3187.292304112601</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>O01→S001(76.0kg,306.9s,2.0100kWh,273.1m); S001→O01(0.0kg,312.5s,0.9661kWh,273.1m)</t>
+          <t>O01→S001(76.0kg,306.9s,1.9601kWh,273.1m); S001→O01(0.0kg,312.5s,0.9661kWh,273.1m)</t>
         </is>
       </c>
     </row>
@@ -3172,14 +3136,14 @@
         <v>0.156</v>
       </c>
       <c r="E9" t="n">
-        <v>65.84816431686254</v>
+        <v>67.57525894245813</v>
       </c>
       <c r="F9" t="n">
-        <v>3134.153658408608</v>
+        <v>3096.733274854037</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>O01→S006(59.0kg,333.1s,1.7398kWh,366.1m); S006→O01(0.0kg,351.8s,0.9924kWh,366.1m)</t>
+          <t>O01→S006(59.0kg,333.1s,1.6016kWh,366.1m); S006→O01(0.0kg,351.8s,0.9924kWh,366.1m)</t>
         </is>
       </c>
     </row>
@@ -3201,14 +3165,14 @@
         <v>0.235</v>
       </c>
       <c r="E10" t="n">
-        <v>62.10113637988734</v>
+        <v>62.44127637498617</v>
       </c>
       <c r="F10" t="n">
-        <v>4842.766005408284</v>
+        <v>4835.396305514476</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>O01→S001(78.0kg,306.9s,2.0658kWh,273.1m); S001→O01(0.0kg,312.5s,0.9661kWh,273.1m)</t>
+          <t>O01→S001(78.0kg,306.9s,2.0385kWh,273.1m); S001→O01(0.0kg,312.5s,0.9661kWh,273.1m)</t>
         </is>
       </c>
     </row>
@@ -3220,24 +3184,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S002-FOD-02,S002-HYG-01,S002-WAT-02,S002-WAT-03,S002-WAT-04</t>
+          <t>S002-FOD-01,S002-FOD-02,S002-HYG-01,S002-WAT-02,S002-WAT-03,S002-WAT-04</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>0.144</v>
+        <v>0.172</v>
       </c>
       <c r="E11" t="n">
-        <v>24.1305898014899</v>
+        <v>23.43715151123657</v>
       </c>
       <c r="F11" t="n">
-        <v>6083.605422582137</v>
+        <v>6164.62991887096</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>O01→S002(56.0kg,612.9s,3.7581kWh,309.0m); S002→O01(0.0kg,622.1s,2.3114kWh,309.0m)</t>
+          <t>O01→S002(64.0kg,612.9s,3.8136kWh,309.0m); S002→O01(0.0kg,622.1s,2.3114kWh,309.0m)</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3213,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S012-FOD-01,S013-FOD-01</t>
+          <t>S010-FOD-01,S014-FOD-01</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3259,14 +3223,14 @@
         <v>0.056</v>
       </c>
       <c r="E12" t="n">
-        <v>32.61926368289379</v>
+        <v>44.89853992152771</v>
       </c>
       <c r="F12" t="n">
-        <v>5326.426019316896</v>
+        <v>5082.875631543558</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>O01→S013(16.0kg,513.5s,1.0892kWh,399.2m); S013→S012(8.0kg,329.6s,0.5758kWh,436.5m); S012→O01(0.0kg,775.3s,1.3671kWh,413.3m)</t>
+          <t>O01→S010(16.0kg,534.5s,1.0585kWh,435.6m); S010→S014(8.0kg,283.1s,0.3833kWh,537.6m); S014→O01(0.0kg,716.9s,1.0378kWh,591.9m)</t>
         </is>
       </c>
     </row>
@@ -3288,14 +3252,14 @@
         <v>0.062</v>
       </c>
       <c r="E13" t="n">
-        <v>57.04269925679174</v>
+        <v>58.59286109905536</v>
       </c>
       <c r="F13" t="n">
-        <v>4623.641965822161</v>
+        <v>4596.772493889592</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>O01→S007(20.0kg,495.7s,1.0304kWh,512.0m); S007→O01(0.0kg,510.5s,0.6879kWh,512.0m)</t>
+          <t>O01→S007(20.0kg,495.7s,0.9684kWh,512.0m); S007→O01(0.0kg,510.5s,0.6879kWh,512.0m)</t>
         </is>
       </c>
     </row>
@@ -3307,24 +3271,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S010-FOD-01,S014-FOD-01</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>0.056</v>
+        <v>0.028</v>
       </c>
       <c r="E14" t="n">
-        <v>44.05666888351266</v>
+        <v>58.42128716966948</v>
       </c>
       <c r="F14" t="n">
-        <v>5135.649016130236</v>
+        <v>4246.401344132762</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>O01→S010(16.0kg,534.5s,1.0866kWh,435.6m); S010→S014(8.0kg,283.1s,0.3930kWh,537.6m); S014→O01(0.0kg,716.9s,1.0378kWh,591.9m)</t>
+          <t>O01→S013(8.0kg,513.5s,0.9857kWh,399.2m); S013→O01(0.0kg,528.5s,0.8853kWh,399.2m)</t>
         </is>
       </c>
     </row>
@@ -3346,14 +3310,14 @@
         <v>0.067</v>
       </c>
       <c r="E15" t="n">
-        <v>28.65825125482107</v>
+        <v>30.5207240136766</v>
       </c>
       <c r="F15" t="n">
-        <v>5803.389832166738</v>
+        <v>5875.018329799617</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>O01→S003(25.0kg,718.1s,1.7614kWh,561.8m); S003→O01(0.0kg,732.1s,1.0922kWh,561.8m)</t>
+          <t>O01→S003(25.0kg,718.1s,1.6869kWh,561.8m); S003→O01(0.0kg,732.1s,1.0922kWh,561.8m)</t>
         </is>
       </c>
     </row>
@@ -3365,24 +3329,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S008-MED-01,S008-FOD-01,S008-HYG-01,S008-WAT-01,S008-WAT-02</t>
+          <t>S004-MED-01,S004-FOD-01,S004-HYG-01,S004-WAT-01,S004-WAT-02,S004-WAT-03</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>0.129</v>
+        <v>0.156</v>
       </c>
       <c r="E16" t="n">
-        <v>22.39755205568741</v>
+        <v>22.788512126358</v>
       </c>
       <c r="F16" t="n">
-        <v>7906.770221852043</v>
+        <v>7999.725022369212</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>O01→S008(45.0kg,689.7s,3.6860kWh,372.9m); S008→O01(0.0kg,704.0s,2.5222kWh,372.9m)</t>
+          <t>O01→S004(59.0kg,709.6s,3.7487kWh,398.2m); S004→O01(0.0kg,719.6s,2.4282kWh,398.2m)</t>
         </is>
       </c>
     </row>
@@ -3404,14 +3368,14 @@
         <v>0.067</v>
       </c>
       <c r="E17" t="n">
-        <v>40.68345249890103</v>
+        <v>42.22736092582247</v>
       </c>
       <c r="F17" t="n">
-        <v>6736.776343974943</v>
+        <v>6710.015264574971</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>O01→S015(25.0kg,588.2s,1.4889kWh,571.8m); S015→O01(0.0kg,611.3s,0.8838kWh,571.8m)</t>
+          <t>O01→S015(25.0kg,588.2s,1.4271kWh,571.8m); S015→O01(0.0kg,611.3s,0.8838kWh,571.8m)</t>
         </is>
       </c>
     </row>
@@ -3423,24 +3387,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S004-MED-01,S004-FOD-01,S004-WAT-02,S004-WAT-03</t>
+          <t>S008-MED-01,S008-FOD-01,S008-HYG-01,S008-WAT-01,S008-WAT-02</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D18" t="n">
-        <v>0.094</v>
+        <v>0.129</v>
       </c>
       <c r="E18" t="n">
-        <v>27.85862449671831</v>
+        <v>26.78128615254341</v>
       </c>
       <c r="F18" t="n">
-        <v>8176.016828986647</v>
+        <v>8295.933557728738</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>O01→S004(39.0kg,709.6s,3.3431kWh,398.2m); S004→O01(0.0kg,719.6s,2.4282kWh,398.2m)</t>
+          <t>O01→S008(45.0kg,689.7s,3.3353kWh,372.9m); S008→O01(0.0kg,704.0s,2.5222kWh,372.9m)</t>
         </is>
       </c>
     </row>
@@ -3452,24 +3416,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S004-HYG-01,S004-WAT-01</t>
+          <t>S009-MED-01,S009-FOD-01,S009-WAT-01</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0.062</v>
+        <v>0.067</v>
       </c>
       <c r="E19" t="n">
-        <v>30.38763163008179</v>
+        <v>47.43860889415698</v>
       </c>
       <c r="F19" t="n">
-        <v>7699.186341710088</v>
+        <v>7142.554782418401</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>O01→S004(20.0kg,674.5s,1.6362kWh,398.2m); S004→O01(0.0kg,681.2s,1.1483kWh,398.2m)</t>
+          <t>O01→S009(25.0kg,462.0s,1.2694kWh,293.2m); S009→O01(0.0kg,468.8s,0.8331kWh,293.2m)</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3445,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S009-MED-01,S009-FOD-01,S009-WAT-01</t>
+          <t>S011-MED-01,S011-FOD-01,S011-WAT-01</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3491,14 +3455,14 @@
         <v>0.067</v>
       </c>
       <c r="E20" t="n">
-        <v>45.97073595485033</v>
+        <v>73.07068411984088</v>
       </c>
       <c r="F20" t="n">
-        <v>8205.909887952264</v>
+        <v>7365.028467109804</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>O01→S009(25.0kg,462.0s,1.3281kWh,293.2m); S009→O01(0.0kg,468.8s,0.8331kWh,293.2m)</t>
+          <t>O01→S011(25.0kg,277.0s,0.6542kWh,295.4m); S011→O01(0.0kg,282.6s,0.4229kWh,295.4m)</t>
         </is>
       </c>
     </row>
@@ -3520,14 +3484,14 @@
         <v>0.144</v>
       </c>
       <c r="E21" t="n">
-        <v>23.92727351087621</v>
+        <v>27.95784513671165</v>
       </c>
       <c r="F21" t="n">
-        <v>10243.43711510204</v>
+        <v>10257.53366525731</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>O01→S003(56.0kg,769.4s,3.7926kWh,561.8m); S003→O01(0.0kg,790.4s,2.2933kWh,561.8m)</t>
+          <t>O01→S003(56.0kg,769.4s,3.4701kWh,561.8m); S003→O01(0.0kg,790.4s,2.2933kWh,561.8m)</t>
         </is>
       </c>
     </row>
@@ -3539,58 +3503,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S011-MED-01,S011-FOD-01,S011-WAT-01</t>
+          <t>S005-MED-01,S005-FOD-01,S005-HYG-01,S005-WAT-01,S005-WAT-02,S005-WAT-03</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D22" t="n">
-        <v>0.067</v>
+        <v>0.156</v>
       </c>
       <c r="E22" t="n">
-        <v>72.37760026663855</v>
+        <v>47.01524949131925</v>
       </c>
       <c r="F22" t="n">
-        <v>8158.039025356808</v>
+        <v>10026.01179698843</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>O01→S011(25.0kg,275.5s,0.6825kWh,293.3m); S011→O01(0.0kg,281.2s,0.4224kWh,293.3m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q2-022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>S005-MED-01,S005-FOD-01,S005-HYG-01,S005-WAT-01,S005-WAT-02,S005-WAT-03</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>59</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="E23" t="n">
-        <v>44.13659668075511</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10007.35811159516</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>O01→S005(59.0kg,498.7s,2.8029kWh,326.4m); S005→O01(0.0kg,505.4s,1.6662kWh,326.4m)</t>
+          <t>O01→S005(59.0kg,498.7s,2.5726kWh,326.4m); S005→O01(0.0kg,505.4s,1.6662kWh,326.4m)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G23"/>
+  <autoFilter ref="A1:G22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3601,7 +3536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3656,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1653.853569215474</v>
+        <v>2007.732659143701</v>
       </c>
       <c r="F2" t="n">
-        <v>2725.64726236731</v>
+        <v>3353.926962117941</v>
       </c>
     </row>
     <row r="3">
@@ -3682,10 +3617,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1612.024508122992</v>
+        <v>1653.853569215474</v>
       </c>
       <c r="F3" t="n">
-        <v>2685.435725695818</v>
+        <v>2717.921318091663</v>
       </c>
     </row>
     <row r="4">
@@ -3708,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2110.416386028363</v>
+        <v>1612.024508122992</v>
       </c>
       <c r="F4" t="n">
-        <v>3477.797518237549</v>
+        <v>2677.596171183992</v>
       </c>
     </row>
     <row r="5">
@@ -3737,7 +3672,7 @@
         <v>1988.962351014692</v>
       </c>
       <c r="F5" t="n">
-        <v>3158.588572679618</v>
+        <v>3149.840017751248</v>
       </c>
     </row>
     <row r="6">
@@ -3760,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1819.890041865742</v>
+        <v>1636.191043136609</v>
       </c>
       <c r="F6" t="n">
-        <v>3699.115613975328</v>
+        <v>3074.10366189224</v>
       </c>
     </row>
     <row r="7">
@@ -3786,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1636.191043136609</v>
+        <v>1923.801400652118</v>
       </c>
       <c r="F7" t="n">
-        <v>3094.261135135178</v>
+        <v>3784.40449342988</v>
       </c>
     </row>
     <row r="8">
@@ -3815,7 +3750,7 @@
         <v>1561.426741698547</v>
       </c>
       <c r="F8" t="n">
-        <v>3200.792776006735</v>
+        <v>3187.292304112601</v>
       </c>
     </row>
     <row r="9">
@@ -3841,7 +3776,7 @@
         <v>1560.863885273963</v>
       </c>
       <c r="F9" t="n">
-        <v>3134.153658408608</v>
+        <v>3096.733274854037</v>
       </c>
     </row>
     <row r="10">
@@ -3867,7 +3802,7 @@
         <v>3188.29062697251</v>
       </c>
       <c r="F10" t="n">
-        <v>4842.766005408284</v>
+        <v>4835.396305514476</v>
       </c>
     </row>
     <row r="11">
@@ -3890,10 +3825,10 @@
         <v>1561.426741698547</v>
       </c>
       <c r="E11" t="n">
-        <v>3606.434868281085</v>
+        <v>3672.434868281085</v>
       </c>
       <c r="F11" t="n">
-        <v>6083.605422582137</v>
+        <v>6164.62991887096</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3839,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3916,10 +3851,10 @@
         <v>1612.024508122992</v>
       </c>
       <c r="E12" t="n">
-        <v>3950.476447194515</v>
+        <v>3866.556650523419</v>
       </c>
       <c r="F12" t="n">
-        <v>5326.426019316896</v>
+        <v>5082.875631543558</v>
       </c>
     </row>
     <row r="13">
@@ -3930,7 +3865,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3945,7 +3880,7 @@
         <v>3212.382086273218</v>
       </c>
       <c r="F13" t="n">
-        <v>4623.641965822161</v>
+        <v>4596.772493889592</v>
       </c>
     </row>
     <row r="14">
@@ -3956,7 +3891,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3968,10 +3903,10 @@
         <v>1653.853569215474</v>
       </c>
       <c r="E14" t="n">
-        <v>3908.385711615901</v>
+        <v>3205.878077338466</v>
       </c>
       <c r="F14" t="n">
-        <v>5135.649016130236</v>
+        <v>4246.401344132762</v>
       </c>
     </row>
     <row r="15">
@@ -3982,7 +3917,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3991,13 +3926,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1819.890041865742</v>
+        <v>1923.801400652118</v>
       </c>
       <c r="E15" t="n">
-        <v>3900.132853916969</v>
+        <v>4004.044212703345</v>
       </c>
       <c r="F15" t="n">
-        <v>5803.389832166738</v>
+        <v>5875.018329799617</v>
       </c>
     </row>
     <row r="16">
@@ -4013,17 +3948,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>3188.29062697251</v>
       </c>
       <c r="E16" t="n">
-        <v>5392.050516391937</v>
+        <v>5493.476118440301</v>
       </c>
       <c r="F16" t="n">
-        <v>7906.770221852043</v>
+        <v>7999.725022369212</v>
       </c>
     </row>
     <row r="17">
@@ -4034,12 +3969,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4049,7 +3984,7 @@
         <v>5041.956187289227</v>
       </c>
       <c r="F17" t="n">
-        <v>6736.776343974943</v>
+        <v>6710.015264574971</v>
       </c>
     </row>
     <row r="18">
@@ -4065,17 +4000,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3606.434868281085</v>
+        <v>3672.434868281085</v>
       </c>
       <c r="E18" t="n">
-        <v>5779.620359748877</v>
+        <v>5876.194757700512</v>
       </c>
       <c r="F18" t="n">
-        <v>8176.016828986647</v>
+        <v>8295.933557728738</v>
       </c>
     </row>
     <row r="19">
@@ -4086,22 +4021,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3900.132853916969</v>
+        <v>4004.044212703345</v>
       </c>
       <c r="E19" t="n">
-        <v>5825.905289964839</v>
+        <v>5564.824003250455</v>
       </c>
       <c r="F19" t="n">
-        <v>7699.186341710088</v>
+        <v>7142.554782418401</v>
       </c>
     </row>
     <row r="20">
@@ -4112,7 +4047,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4124,10 +4059,10 @@
         <v>5041.956187289227</v>
       </c>
       <c r="E20" t="n">
-        <v>6602.735977836337</v>
+        <v>6231.586991853713</v>
       </c>
       <c r="F20" t="n">
-        <v>8205.909887952264</v>
+        <v>7365.028467109804</v>
       </c>
     </row>
     <row r="21">
@@ -4147,13 +4082,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5392.050516391937</v>
+        <v>5493.476118440301</v>
       </c>
       <c r="E21" t="n">
-        <v>7761.861374504362</v>
+        <v>7863.286976552727</v>
       </c>
       <c r="F21" t="n">
-        <v>10243.43711510204</v>
+        <v>10257.53366525731</v>
       </c>
     </row>
     <row r="22">
@@ -4164,52 +4099,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5825.905289964839</v>
+        <v>6164.62991887096</v>
       </c>
       <c r="E22" t="n">
-        <v>7012.58409664521</v>
+        <v>8044.675535967012</v>
       </c>
       <c r="F22" t="n">
-        <v>8158.039025356808</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q2-022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>C-BAT-04</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>6083.605422582137</v>
-      </c>
-      <c r="E23" t="n">
-        <v>7963.65103967819</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10007.35811159516</v>
+        <v>10026.01179698843</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F23"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4268,7 +4177,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S010-MED-01</t>
+          <t>S002-MED-01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4278,7 +4187,7 @@
         <v>3600</v>
       </c>
       <c r="D2" t="n">
-        <v>1104.463451274404</v>
+        <v>1285.80632957185</v>
       </c>
       <c r="E2" t="n">
         <v>3600</v>
@@ -4298,7 +4207,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S010-WAT-01</t>
+          <t>S002-WAT-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4308,7 +4217,7 @@
         <v>3600</v>
       </c>
       <c r="D3" t="n">
-        <v>1104.463451274404</v>
+        <v>1285.80632957185</v>
       </c>
       <c r="E3" t="n">
         <v>3600</v>
@@ -4328,7 +4237,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S013-MED-01</t>
+          <t>S010-MED-01</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4338,7 +4247,7 @@
         <v>3600</v>
       </c>
       <c r="D4" t="n">
-        <v>1083.545587394829</v>
+        <v>1104.463451274404</v>
       </c>
       <c r="E4" t="n">
         <v>3600</v>
@@ -4358,7 +4267,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S013-WAT-01</t>
+          <t>S010-WAT-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4368,7 +4277,7 @@
         <v>3600</v>
       </c>
       <c r="D5" t="n">
-        <v>1083.545587394829</v>
+        <v>1104.463451274404</v>
       </c>
       <c r="E5" t="n">
         <v>3600</v>
@@ -4388,17 +4297,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S012-MED-01</t>
+          <t>S013-MED-01</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3600</v>
       </c>
       <c r="C6" t="n">
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="D6" t="n">
-        <v>1335.138193014182</v>
+        <v>1083.545587394829</v>
       </c>
       <c r="E6" t="n">
         <v>3600</v>
@@ -4412,13 +4321,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S012-WAT-01</t>
+          <t>S013-WAT-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4428,7 +4337,7 @@
         <v>3600</v>
       </c>
       <c r="D7" t="n">
-        <v>1335.138193014182</v>
+        <v>1083.545587394829</v>
       </c>
       <c r="E7" t="n">
         <v>3600</v>
@@ -4508,14 +4417,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S002-FOD-01</t>
+          <t>S007-FOD-01</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>7200</v>
       </c>
       <c r="D10" t="n">
-        <v>1221.885020932871</v>
+        <v>1125.735521568304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4532,7 +4441,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S002-MED-01</t>
+          <t>S007-MED-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4542,7 +4451,7 @@
         <v>3600</v>
       </c>
       <c r="D11" t="n">
-        <v>1221.885020932871</v>
+        <v>1125.735521568304</v>
       </c>
       <c r="E11" t="n">
         <v>3600</v>
@@ -4562,7 +4471,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S002-WAT-01</t>
+          <t>S007-WAT-01</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4572,7 +4481,7 @@
         <v>3600</v>
       </c>
       <c r="D12" t="n">
-        <v>1221.885020932871</v>
+        <v>1125.735521568304</v>
       </c>
       <c r="E12" t="n">
         <v>3600</v>
@@ -4592,14 +4501,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S007-FOD-01</t>
+          <t>S012-FOD-01</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>7200</v>
       </c>
       <c r="D13" t="n">
-        <v>1125.735521568304</v>
+        <v>1271.830700326059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4616,17 +4525,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S012-MED-01</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3600</v>
       </c>
       <c r="C14" t="n">
-        <v>3600</v>
+        <v>7200</v>
       </c>
       <c r="D14" t="n">
-        <v>1125.735521568304</v>
+        <v>1271.830700326059</v>
       </c>
       <c r="E14" t="n">
         <v>3600</v>
@@ -4640,13 +4549,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S007-WAT-01</t>
+          <t>S012-WAT-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4656,7 +4565,7 @@
         <v>3600</v>
       </c>
       <c r="D15" t="n">
-        <v>1125.735521568304</v>
+        <v>1271.830700326059</v>
       </c>
       <c r="E15" t="n">
         <v>3600</v>
@@ -5207,14 +5116,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S002-FOD-02</t>
+          <t>S002-FOD-01</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>7200</v>
       </c>
       <c r="D37" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5231,14 +5140,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S002-FOD-02</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="D38" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5249,20 +5158,20 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S002-WAT-02</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="D39" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5273,20 +5182,20 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S002-WAT-03</t>
+          <t>S002-WAT-02</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3600</v>
       </c>
       <c r="D40" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5303,14 +5212,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S002-WAT-04</t>
+          <t>S002-WAT-03</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>3600</v>
       </c>
       <c r="D41" t="n">
-        <v>2984.340804989816</v>
+        <v>3050.340804989816</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5327,14 +5236,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S012-FOD-01</t>
+          <t>S002-WAT-04</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="D42" t="n">
-        <v>3175.198254180334</v>
+        <v>3050.340804989816</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5345,20 +5254,20 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S013-FOD-01</t>
+          <t>S010-FOD-01</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>7200</v>
       </c>
       <c r="D43" t="n">
-        <v>2665.570095517821</v>
+        <v>2686.487959397396</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5375,14 +5284,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S014-FOD-01</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="D44" t="n">
-        <v>2701.926564704913</v>
+        <v>3149.63214168274</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5393,17 +5302,17 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S007-WAT-02</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3600</v>
+        <v>10800</v>
       </c>
       <c r="D45" t="n">
         <v>2701.926564704913</v>
@@ -5417,20 +5326,20 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S010-FOD-01</t>
+          <t>S007-WAT-02</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7200</v>
+        <v>3600</v>
       </c>
       <c r="D46" t="n">
-        <v>2728.317020489878</v>
+        <v>2701.926564704913</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5441,20 +5350,20 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S014-FOD-01</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>7200</v>
       </c>
       <c r="D47" t="n">
-        <v>3191.461202775222</v>
+        <v>2677.399156610303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5478,7 +5387,7 @@
         <v>10800</v>
       </c>
       <c r="D48" t="n">
-        <v>3167.984781224689</v>
+        <v>3271.896140011065</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5505,7 +5414,7 @@
         <v>7200</v>
       </c>
       <c r="D49" t="n">
-        <v>3167.984781224689</v>
+        <v>3271.896140011065</v>
       </c>
       <c r="E49" t="n">
         <v>7200</v>
@@ -5535,7 +5444,7 @@
         <v>7200</v>
       </c>
       <c r="D50" t="n">
-        <v>3167.984781224689</v>
+        <v>3271.896140011065</v>
       </c>
       <c r="E50" t="n">
         <v>7200</v>
@@ -5555,14 +5464,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S004-FOD-01</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>10800</v>
       </c>
       <c r="D51" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5579,14 +5488,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S004-HYG-01</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>14400</v>
       </c>
       <c r="D52" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5603,7 +5512,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S008-MED-01</t>
+          <t>S004-MED-01</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -5613,7 +5522,7 @@
         <v>7200</v>
       </c>
       <c r="D53" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
       <c r="E53" t="n">
         <v>7200</v>
@@ -5633,7 +5542,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S008-WAT-01</t>
+          <t>S004-WAT-01</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -5643,7 +5552,7 @@
         <v>7200</v>
       </c>
       <c r="D54" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
       <c r="E54" t="n">
         <v>7200</v>
@@ -5663,14 +5572,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S008-WAT-02</t>
+          <t>S004-WAT-02</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>7200</v>
       </c>
       <c r="D55" t="n">
-        <v>4688.010571682224</v>
+        <v>4773.853372706406</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5687,14 +5596,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S015-FOD-01</t>
+          <t>S004-WAT-03</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14400</v>
+        <v>7200</v>
       </c>
       <c r="D56" t="n">
-        <v>4430.609136781222</v>
+        <v>4773.853372706406</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5705,27 +5614,21 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>7200</v>
+          <t>S015-FOD-01</t>
+        </is>
       </c>
       <c r="C57" t="n">
-        <v>7200</v>
+        <v>14400</v>
       </c>
       <c r="D57" t="n">
         <v>4430.609136781222</v>
       </c>
-      <c r="E57" t="n">
-        <v>7200</v>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>是</t>
@@ -5735,26 +5638,26 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="C58" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="D58" t="n">
         <v>4430.609136781222</v>
       </c>
       <c r="E58" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5765,20 +5668,26 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S004-FOD-01</t>
-        </is>
+          <t>S015-WAT-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>10800</v>
       </c>
       <c r="C59" t="n">
         <v>10800</v>
       </c>
       <c r="D59" t="n">
-        <v>5059.997614014981</v>
+        <v>4430.609136781222</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10800</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5795,20 +5704,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S004-MED-01</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>7200</v>
+          <t>S008-FOD-01</t>
+        </is>
       </c>
       <c r="C60" t="n">
-        <v>7200</v>
+        <v>10800</v>
       </c>
       <c r="D60" t="n">
-        <v>5059.997614014981</v>
-      </c>
-      <c r="E60" t="n">
-        <v>7200</v>
+        <v>5172.154812990799</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5819,20 +5722,20 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S004-WAT-02</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7200</v>
+        <v>14400</v>
       </c>
       <c r="D61" t="n">
-        <v>5059.997614014981</v>
+        <v>5172.154812990799</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5843,20 +5746,26 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S004-WAT-03</t>
-        </is>
+          <t>S008-MED-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>7200</v>
       </c>
       <c r="C62" t="n">
         <v>7200</v>
       </c>
       <c r="D62" t="n">
-        <v>5059.997614014981</v>
+        <v>5172.154812990799</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7200</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5867,20 +5776,26 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S004-HYG-01</t>
-        </is>
+          <t>S008-WAT-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7200</v>
       </c>
       <c r="C63" t="n">
-        <v>14400</v>
+        <v>7200</v>
       </c>
       <c r="D63" t="n">
-        <v>5144.66573860757</v>
+        <v>5172.154812990799</v>
+      </c>
+      <c r="E63" t="n">
+        <v>7200</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5891,26 +5806,20 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S004-WAT-01</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>7200</v>
+          <t>S008-WAT-02</t>
+        </is>
       </c>
       <c r="C64" t="n">
         <v>7200</v>
       </c>
       <c r="D64" t="n">
-        <v>5144.66573860757</v>
-      </c>
-      <c r="E64" t="n">
-        <v>7200</v>
+        <v>5172.154812990799</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5934,7 +5843,7 @@
         <v>14400</v>
       </c>
       <c r="D65" t="n">
-        <v>6133.936082562783</v>
+        <v>5096.0241079769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5961,7 +5870,7 @@
         <v>10800</v>
       </c>
       <c r="D66" t="n">
-        <v>6133.936082562783</v>
+        <v>5096.0241079769</v>
       </c>
       <c r="E66" t="n">
         <v>10800</v>
@@ -5991,7 +5900,7 @@
         <v>10800</v>
       </c>
       <c r="D67" t="n">
-        <v>6133.936082562783</v>
+        <v>5096.0241079769</v>
       </c>
       <c r="E67" t="n">
         <v>10800</v>
@@ -6011,14 +5920,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S003-FOD-02</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10800</v>
+        <v>14400</v>
       </c>
       <c r="D68" t="n">
-        <v>6971.41594544815</v>
+        <v>5948.958256238137</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6029,20 +5938,26 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
-        </is>
+          <t>S011-MED-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10800</v>
       </c>
       <c r="C69" t="n">
-        <v>14400</v>
+        <v>10800</v>
       </c>
       <c r="D69" t="n">
-        <v>6971.41594544815</v>
+        <v>5948.958256238137</v>
+      </c>
+      <c r="E69" t="n">
+        <v>10800</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6053,20 +5968,26 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S003-WAT-02</t>
-        </is>
+          <t>S011-WAT-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>10800</v>
       </c>
       <c r="C70" t="n">
-        <v>7200</v>
+        <v>10800</v>
       </c>
       <c r="D70" t="n">
-        <v>6971.41594544815</v>
+        <v>5948.958256238137</v>
+      </c>
+      <c r="E70" t="n">
+        <v>10800</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6077,20 +5998,20 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S003-WAT-03</t>
+          <t>S003-FOD-02</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7200</v>
+        <v>10800</v>
       </c>
       <c r="D71" t="n">
-        <v>6971.41594544815</v>
+        <v>7072.841547496514</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6101,20 +6022,20 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S003-WAT-04</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7200</v>
+        <v>14400</v>
       </c>
       <c r="D72" t="n">
-        <v>6971.41594544815</v>
+        <v>7072.841547496514</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6125,20 +6046,20 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S011-FOD-01</t>
+          <t>S003-WAT-02</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>14400</v>
+        <v>7200</v>
       </c>
       <c r="D73" t="n">
-        <v>6731.431359971691</v>
+        <v>7072.841547496514</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6149,26 +6070,20 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S011-MED-01</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>10800</v>
+          <t>S003-WAT-03</t>
+        </is>
       </c>
       <c r="C74" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="D74" t="n">
-        <v>6731.431359971691</v>
-      </c>
-      <c r="E74" t="n">
-        <v>10800</v>
+        <v>7072.841547496514</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6179,26 +6094,20 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S011-WAT-01</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>10800</v>
+          <t>S003-WAT-04</t>
+        </is>
       </c>
       <c r="C75" t="n">
-        <v>10800</v>
+        <v>7200</v>
       </c>
       <c r="D75" t="n">
-        <v>6731.431359971691</v>
-      </c>
-      <c r="E75" t="n">
-        <v>10800</v>
+        <v>7072.841547496514</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6209,7 +6118,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -6222,7 +6131,7 @@
         <v>14400</v>
       </c>
       <c r="D76" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6246,7 +6155,7 @@
         <v>18000</v>
       </c>
       <c r="D77" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6273,7 +6182,7 @@
         <v>10800</v>
       </c>
       <c r="D78" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
       <c r="E78" t="n">
         <v>10800</v>
@@ -6303,7 +6212,7 @@
         <v>10800</v>
       </c>
       <c r="D79" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
       <c r="E79" t="n">
         <v>10800</v>
@@ -6330,7 +6239,7 @@
         <v>10800</v>
       </c>
       <c r="D80" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6354,7 +6263,7 @@
         <v>10800</v>
       </c>
       <c r="D81" t="n">
-        <v>7458.263231130163</v>
+        <v>7539.287727418986</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6390,7 +6299,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -6400,7 +6309,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -6440,7 +6349,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7963.65103967819</v>
+        <v>8044.675535967012</v>
       </c>
     </row>
     <row r="7">
@@ -6450,7 +6359,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.79800333426023</v>
+        <v>64.62525880271696</v>
       </c>
     </row>
     <row r="8">
